--- a/data/trans_camb/IMC_inf_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 22,82</t>
+          <t>-2,91; 23,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 9,38</t>
+          <t>-15,75; 9,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,31; -0,9</t>
+          <t>-23,38; -0,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 24,36</t>
+          <t>0,32; 25,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 22,5</t>
+          <t>-2,29; 22,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 2,54</t>
+          <t>-20,65; 3,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 20,27</t>
+          <t>1,03; 20,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 13,32</t>
+          <t>-5,33; 12,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,86; -2,18</t>
+          <t>-18,23; -2,13</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 79,31</t>
+          <t>-7,04; 83,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 29,52</t>
+          <t>-38,9; 34,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,05; -2,94</t>
+          <t>-57,23; 0,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 81,26</t>
+          <t>0,44; 82,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 75,13</t>
+          <t>-5,15; 83,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 9,59</t>
+          <t>-48,01; 9,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 65,04</t>
+          <t>2,49; 65,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 42,65</t>
+          <t>-13,7; 39,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,98; -7,08</t>
+          <t>-45,14; -6,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 14,11</t>
+          <t>-11,2; 13,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 2,09</t>
+          <t>-21,15; 2,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 9,04</t>
+          <t>-15,34; 8,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 29,62</t>
+          <t>5,22; 30,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 12,75</t>
+          <t>-11,13; 12,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 16,01</t>
+          <t>-9,75; 16,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 19,24</t>
+          <t>0,85; 19,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 4,78</t>
+          <t>-13,12; 3,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 9,76</t>
+          <t>-9,02; 8,53</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 56,95</t>
+          <t>-29,26; 51,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 8,14</t>
+          <t>-55,46; 9,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 34,33</t>
+          <t>-39,55; 33,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 92,76</t>
+          <t>11,42; 95,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 43,72</t>
+          <t>-25,02; 40,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 50,79</t>
+          <t>-23,18; 52,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 62,53</t>
+          <t>1,52; 63,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 15,46</t>
+          <t>-33,01; 12,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 32,9</t>
+          <t>-22,27; 27,86</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 17,72</t>
+          <t>-11,08; 15,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 12,81</t>
+          <t>-16,91; 10,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 17,78</t>
+          <t>-12,46; 17,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 11,69</t>
+          <t>-15,73; 11,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 9,74</t>
+          <t>-18,35; 9,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 7,58</t>
+          <t>-20,61; 9,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 8,31</t>
+          <t>-11,92; 8,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 5,09</t>
+          <t>-14,28; 6,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 6,94</t>
+          <t>-15,21; 7,67</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 68,88</t>
+          <t>-28,35; 68,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,21; 52,85</t>
+          <t>-43,11; 40,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 71,65</t>
+          <t>-33,74; 66,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 26,68</t>
+          <t>-27,87; 25,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 21,66</t>
+          <t>-32,97; 20,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,52; 17,89</t>
+          <t>-37,94; 19,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 20,96</t>
+          <t>-25,51; 21,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,42; 13,26</t>
+          <t>-30,27; 16,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 16,98</t>
+          <t>-32,03; 19,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 14,09</t>
+          <t>-3,3; 14,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 11,74</t>
+          <t>-5,54; 11,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 2,25</t>
+          <t>-21,66; 2,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 15,16</t>
+          <t>-3,18; 14,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 1,91</t>
+          <t>-16,81; 0,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 6,51</t>
+          <t>-13,19; 6,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 12,21</t>
+          <t>-0,3; 12,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 3,59</t>
+          <t>-8,65; 3,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 1,67</t>
+          <t>-15,37; 1,56</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 41,15</t>
+          <t>-7,85; 41,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 34,76</t>
+          <t>-13,5; 33,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 5,75</t>
+          <t>-51,73; 5,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 34,94</t>
+          <t>-6,52; 32,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 4,04</t>
+          <t>-32,26; 1,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 15,26</t>
+          <t>-26,08; 13,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 30,27</t>
+          <t>-0,31; 30,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 9,03</t>
+          <t>-18,71; 9,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 3,68</t>
+          <t>-33,33; 3,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 16,76</t>
+          <t>-6,23; 16,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 4,35</t>
+          <t>-16,92; 4,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 3,65</t>
+          <t>-20,34; 2,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 11,97</t>
+          <t>-11,31; 11,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 15,6</t>
+          <t>-5,96; 15,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 7,4</t>
+          <t>-15,42; 8,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 11,49</t>
+          <t>-4,68; 10,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 7,2</t>
+          <t>-7,87; 7,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 3,04</t>
+          <t>-14,5; 2,74</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 46,43</t>
+          <t>-12,15; 44,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 12,11</t>
+          <t>-34,47; 13,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 10,39</t>
+          <t>-42,93; 6,12</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 33,83</t>
+          <t>-23,99; 30,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 40,67</t>
+          <t>-12,14; 44,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,3; 19,28</t>
+          <t>-33,74; 21,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 30,5</t>
+          <t>-10,13; 28,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 18,01</t>
+          <t>-16,98; 20,5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 7,88</t>
+          <t>-31,43; 7,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,19; 31,93</t>
+          <t>1,28; 32,25</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 21,46</t>
+          <t>-6,68; 21,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 2,53</t>
+          <t>-21,79; 3,31</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 10,52</t>
+          <t>-21,07; 9,89</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 7,46</t>
+          <t>-20,19; 9,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-34,49; -4,35</t>
+          <t>-34,45; -4,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 19,2</t>
+          <t>-3,56; 17,67</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 13,17</t>
+          <t>-9,26; 11,34</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-22,8; -3,03</t>
+          <t>-23,82; -3,21</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2,17; 148,32</t>
+          <t>2,74; 155,54</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 98,64</t>
+          <t>-20,88; 102,19</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 16,03</t>
+          <t>-68,67; 14,21</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 22,52</t>
+          <t>-34,36; 20,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 15,55</t>
+          <t>-32,84; 19,37</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,39; -9,03</t>
+          <t>-56,72; -10,19</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 54,56</t>
+          <t>-7,31; 50,62</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 37,04</t>
+          <t>-20,71; 32,03</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-52,06; -7,39</t>
+          <t>-54,07; -7,75</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,47; 11,22</t>
+          <t>1,59; 11,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 3,76</t>
+          <t>-6,05; 3,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,3; -2,17</t>
+          <t>-12,18; -1,54</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,58; 10,2</t>
+          <t>0,57; 10,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 2,99</t>
+          <t>-6,79; 3,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,51; -1,39</t>
+          <t>-11,2; -0,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,66</t>
+          <t>2,4; 9,31</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,34</t>
+          <t>-4,83; 1,98</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -2,93</t>
+          <t>-10,68; -2,55</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,85; 34,07</t>
+          <t>3,73; 34,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 11,41</t>
+          <t>-15,71; 10,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,35; -6,53</t>
+          <t>-32,94; -4,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,31; 23,82</t>
+          <t>1,14; 24,04</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 7,01</t>
+          <t>-14,1; 7,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-24,33; -3,01</t>
+          <t>-23,72; -0,92</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,33; 24,82</t>
+          <t>5,71; 24,05</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 6,03</t>
+          <t>-11,26; 5,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,64; -7,56</t>
+          <t>-25,09; -6,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 23,13</t>
+          <t>-2,97; 22,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 9,49</t>
+          <t>-16,13; 10,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,38; -0,48</t>
+          <t>-22,39; -0,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 25,74</t>
+          <t>-1,2; 25,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 22,99</t>
+          <t>-4,28; 20,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 3,15</t>
+          <t>-20,63; 3,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 20,71</t>
+          <t>1,59; 20,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 12,42</t>
+          <t>-5,59; 12,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,23; -2,13</t>
+          <t>-18,12; -1,42</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 83,19</t>
+          <t>-8,47; 79,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,9; 34,14</t>
+          <t>-40,06; 39,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 0,06</t>
+          <t>-56,62; -1,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 82,17</t>
+          <t>-3,04; 83,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 83,43</t>
+          <t>-9,81; 67,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,01; 9,76</t>
+          <t>-49,14; 11,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 65,63</t>
+          <t>3,58; 65,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 39,73</t>
+          <t>-13,94; 40,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,14; -6,28</t>
+          <t>-46,03; -3,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 13,67</t>
+          <t>-11,66; 13,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 2,64</t>
+          <t>-20,35; 3,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 8,85</t>
+          <t>-15,08; 8,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 30,28</t>
+          <t>4,82; 30,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 12,19</t>
+          <t>-12,64; 11,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 16,49</t>
+          <t>-10,42; 17,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 19,04</t>
+          <t>0,94; 19,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 3,89</t>
+          <t>-13,01; 3,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 8,53</t>
+          <t>-8,87; 8,99</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 51,39</t>
+          <t>-29,38; 53,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 9,0</t>
+          <t>-52,97; 14,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,55; 33,66</t>
+          <t>-38,91; 32,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,42; 95,88</t>
+          <t>10,56; 98,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 40,33</t>
+          <t>-28,16; 36,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 52,92</t>
+          <t>-23,11; 57,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 63,03</t>
+          <t>1,69; 61,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 12,46</t>
+          <t>-33,05; 12,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 27,86</t>
+          <t>-22,38; 29,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 15,96</t>
+          <t>-11,62; 14,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 10,77</t>
+          <t>-15,84; 12,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 17,06</t>
+          <t>-13,57; 17,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 11,58</t>
+          <t>-13,86; 11,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 9,2</t>
+          <t>-16,53; 9,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 9,27</t>
+          <t>-21,87; 7,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 8,18</t>
+          <t>-10,2; 8,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 6,56</t>
+          <t>-14,45; 5,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 7,67</t>
+          <t>-14,81; 6,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 68,53</t>
+          <t>-29,74; 57,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,11; 40,38</t>
+          <t>-42,1; 48,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 66,38</t>
+          <t>-36,34; 68,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 25,43</t>
+          <t>-24,95; 27,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 20,03</t>
+          <t>-29,95; 21,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,94; 19,44</t>
+          <t>-39,98; 16,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 21,17</t>
+          <t>-21,49; 23,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,27; 16,53</t>
+          <t>-30,95; 14,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 19,61</t>
+          <t>-32,01; 17,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 14,47</t>
+          <t>-3,63; 14,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 11,7</t>
+          <t>-5,95; 11,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 2,05</t>
+          <t>-20,87; 2,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 14,6</t>
+          <t>-2,63; 14,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 0,95</t>
+          <t>-16,08; 1,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 6,17</t>
+          <t>-13,76; 6,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 12,22</t>
+          <t>-1,04; 12,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 3,62</t>
+          <t>-8,55; 4,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 1,56</t>
+          <t>-15,34; 1,82</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 41,86</t>
+          <t>-8,64; 45,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 33,9</t>
+          <t>-13,98; 34,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,73; 5,57</t>
+          <t>-51,32; 6,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 32,91</t>
+          <t>-4,96; 34,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 1,73</t>
+          <t>-31,15; 2,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 13,27</t>
+          <t>-26,06; 14,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 30,39</t>
+          <t>-1,95; 29,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 9,13</t>
+          <t>-18,59; 10,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 3,88</t>
+          <t>-33,4; 4,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 16,22</t>
+          <t>-6,49; 17,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 4,88</t>
+          <t>-17,26; 5,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 2,28</t>
+          <t>-19,8; 4,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 11,76</t>
+          <t>-11,68; 11,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 15,82</t>
+          <t>-5,64; 16,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 8,24</t>
+          <t>-16,22; 8,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 10,92</t>
+          <t>-4,5; 11,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 7,98</t>
+          <t>-8,0; 7,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 2,74</t>
+          <t>-14,87; 2,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 44,85</t>
+          <t>-12,2; 47,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 13,25</t>
+          <t>-35,7; 13,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 6,12</t>
+          <t>-42,04; 11,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 30,93</t>
+          <t>-24,74; 31,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 44,15</t>
+          <t>-11,69; 42,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 21,9</t>
+          <t>-34,62; 22,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 28,58</t>
+          <t>-9,48; 29,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 20,5</t>
+          <t>-17,29; 19,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 7,66</t>
+          <t>-31,57; 5,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,28; 32,25</t>
+          <t>2,1; 33,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 21,48</t>
+          <t>-7,96; 21,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 3,31</t>
+          <t>-22,52; 2,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 9,89</t>
+          <t>-19,78; 11,1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 9,28</t>
+          <t>-23,62; 8,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-34,45; -4,59</t>
+          <t>-35,79; -5,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 17,67</t>
+          <t>-3,34; 18,68</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 11,34</t>
+          <t>-8,37; 13,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-23,82; -3,21</t>
+          <t>-23,32; -3,66</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2,74; 155,54</t>
+          <t>4,29; 163,64</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 102,19</t>
+          <t>-23,46; 109,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-68,67; 14,21</t>
+          <t>-68,62; 12,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 20,57</t>
+          <t>-32,8; 22,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 19,37</t>
+          <t>-37,03; 17,51</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,72; -10,19</t>
+          <t>-57,57; -10,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 50,62</t>
+          <t>-7,44; 54,53</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 32,03</t>
+          <t>-19,08; 38,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-54,07; -7,75</t>
+          <t>-51,96; -8,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,59; 11,55</t>
+          <t>1,89; 11,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 3,53</t>
+          <t>-5,75; 3,87</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,18; -1,54</t>
+          <t>-13,04; -2,05</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,57; 10,23</t>
+          <t>0,67; 10,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 3,03</t>
+          <t>-6,27; 3,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,2; -0,37</t>
+          <t>-12,08; -1,28</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,31</t>
+          <t>2,39; 9,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,98</t>
+          <t>-5,38; 1,8</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -2,55</t>
+          <t>-10,34; -2,54</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,73; 34,53</t>
+          <t>5,23; 33,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 10,73</t>
+          <t>-15,03; 11,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-32,94; -4,76</t>
+          <t>-34,26; -6,24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,14; 24,04</t>
+          <t>1,41; 23,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 7,18</t>
+          <t>-13,0; 7,15</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-23,72; -0,92</t>
+          <t>-25,56; -2,94</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,71; 24,05</t>
+          <t>5,54; 24,14</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 5,0</t>
+          <t>-12,45; 4,61</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,09; -6,49</t>
+          <t>-24,75; -6,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-7,6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,62</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-12,34</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,76</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,69</t>
+          <t>-12,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-10,29</t>
+          <t>-9,72</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 22,86</t>
+          <t>-0,78; 24,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 10,89</t>
+          <t>-2,6; 22,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,39; -0,54</t>
+          <t>-19,57; 3,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 25,41</t>
+          <t>-3,59; 22,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 20,16</t>
+          <t>-15,71; 9,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 3,27</t>
+          <t>-22,61; -0,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 20,38</t>
+          <t>2,54; 20,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 12,46</t>
+          <t>-4,87; 13,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,12; -1,42</t>
+          <t>-18,09; -1,61</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35,17%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-20,95%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>26,29%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-10,29%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-35,13%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>25,92%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-23,95%</t>
+          <t>-34,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-28,84%</t>
+          <t>-27,22%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 79,33</t>
+          <t>-1,81; 81,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,06; 39,63</t>
+          <t>-5,68; 75,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,62; -1,87</t>
+          <t>-46,25; 11,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 83,32</t>
+          <t>-7,81; 79,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 67,11</t>
+          <t>-40,44; 29,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,14; 11,17</t>
+          <t>-56,41; -2,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 65,14</t>
+          <t>6,73; 65,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 40,25</t>
+          <t>-12,88; 42,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-46,03; -3,54</t>
+          <t>-46,17; -4,79</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,11</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,56</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-9,64</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,86</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,65</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>-3,09</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 13,63</t>
+          <t>5,13; 29,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 3,27</t>
+          <t>-12,11; 12,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 8,92</t>
+          <t>-9,13; 16,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 30,65</t>
+          <t>-11,63; 14,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 11,55</t>
+          <t>-21,86; 2,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 17,53</t>
+          <t>-15,54; 9,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 19,03</t>
+          <t>0,95; 19,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 3,72</t>
+          <t>-12,09; 4,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 8,99</t>
+          <t>-8,13; 9,76</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46,27%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-0,29%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-29,39%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-8,71%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46,27%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,29%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>-9,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 53,33</t>
+          <t>11,12; 92,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 14,3</t>
+          <t>-27,71; 43,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,91; 32,44</t>
+          <t>-20,22; 53,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 98,65</t>
+          <t>-30,28; 56,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 36,46</t>
+          <t>-54,94; 8,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 57,02</t>
+          <t>-40,07; 33,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 61,68</t>
+          <t>2,73; 62,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 12,43</t>
+          <t>-30,69; 15,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 29,58</t>
+          <t>-20,68; 31,55</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,19</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-6,16</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,37</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,14</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,19</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,54</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-3,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 14,14</t>
+          <t>-14,77; 11,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 12,36</t>
+          <t>-16,89; 9,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 17,15</t>
+          <t>-20,29; 8,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 11,93</t>
+          <t>-11,52; 17,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 9,7</t>
+          <t>-16,42; 12,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 7,93</t>
+          <t>-13,55; 18,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 8,64</t>
+          <t>-11,21; 8,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 5,39</t>
+          <t>-13,15; 5,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 6,82</t>
+          <t>-13,58; 7,07</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-2,62%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-8,29%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-12,19%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>7,06%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-7,31%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-2,62%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-8,29%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-12,93%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-8,03%</t>
+          <t>-8,81%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 57,02</t>
+          <t>-26,5; 26,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,1; 48,97</t>
+          <t>-30,06; 21,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,34; 68,5</t>
+          <t>-36,27; 20,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 27,04</t>
+          <t>-29,24; 68,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 21,46</t>
+          <t>-42,21; 52,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 16,71</t>
+          <t>-35,26; 70,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 23,41</t>
+          <t>-23,34; 20,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,95; 14,01</t>
+          <t>-28,42; 13,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 17,8</t>
+          <t>-29,16; 17,78</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-7,79</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,78</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,58</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-7,79</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,91</t>
+          <t>-4,64</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,96</t>
+          <t>-4,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 14,94</t>
+          <t>-2,76; 15,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 11,05</t>
+          <t>-16,66; 1,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 2,64</t>
+          <t>-13,35; 5,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 14,79</t>
+          <t>-3,82; 14,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 1,15</t>
+          <t>-5,44; 11,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 6,51</t>
+          <t>-13,05; 4,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 12,07</t>
+          <t>-0,28; 12,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 4,32</t>
+          <t>-9,3; 3,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 1,82</t>
+          <t>-10,39; 2,9</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-16,07%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-8,65%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>13,97%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>7,29%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-19,9%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-16,07%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-8,06%</t>
+          <t>-12,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-13,76%</t>
+          <t>-9,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 45,68</t>
+          <t>-5,28; 34,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 34,13</t>
+          <t>-32,32; 4,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,32; 6,45</t>
+          <t>-25,97; 13,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 34,53</t>
+          <t>-9,6; 41,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 2,53</t>
+          <t>-12,98; 34,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 14,64</t>
+          <t>-30,92; 12,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 29,49</t>
+          <t>-0,87; 30,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 10,73</t>
+          <t>-19,5; 9,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,4; 4,57</t>
+          <t>-22,96; 7,01</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5,09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-3,9</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-6,03</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-9,12</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,09</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-11,19</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,87</t>
+          <t>-7,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 17,13</t>
+          <t>-10,8; 11,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 5,55</t>
+          <t>-6,37; 15,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 4,07</t>
+          <t>-16,21; 7,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 11,4</t>
+          <t>-5,94; 16,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 16,21</t>
+          <t>-18,53; 4,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 8,63</t>
+          <t>-23,57; 1,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 11,21</t>
+          <t>-4,17; 11,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 7,68</t>
+          <t>-8,49; 7,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 2,09</t>
+          <t>-15,1; 1,83</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-9,13%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>13,74%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-14,05%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-21,26%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-8,46%</t>
+          <t>-26,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-13,71%</t>
+          <t>-16,43%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 47,11</t>
+          <t>-22,32; 33,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 13,75</t>
+          <t>-12,95; 40,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,04; 11,9</t>
+          <t>-34,43; 18,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,74; 31,5</t>
+          <t>-12,12; 46,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 42,69</t>
+          <t>-36,68; 12,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 22,75</t>
+          <t>-47,32; 3,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 29,05</t>
+          <t>-8,72; 30,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 19,6</t>
+          <t>-18,15; 18,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 5,19</t>
+          <t>-32,66; 4,55</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-4,72</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-7,06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-18,44</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>17,31</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>7,24</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-10,32</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-4,72</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-7,06</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-20,31</t>
+          <t>-11,21</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-13,66</t>
+          <t>-13,52</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,1; 33,68</t>
+          <t>-19,77; 10,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 21,69</t>
+          <t>-23,04; 7,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 2,28</t>
+          <t>-33,31; -2,32</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 11,1</t>
+          <t>1,19; 31,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 8,2</t>
+          <t>-6,36; 21,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-35,79; -5,77</t>
+          <t>-21,96; 1,55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 18,68</t>
+          <t>-2,78; 19,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 13,22</t>
+          <t>-8,15; 13,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-23,32; -3,66</t>
+          <t>-22,96; -2,8</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-8,46%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-12,67%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-33,08%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>64,43%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>26,95%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-38,41%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-8,46%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-12,67%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-36,44%</t>
+          <t>-41,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-34,03%</t>
+          <t>-33,66%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4,29; 163,64</t>
+          <t>-32,17; 22,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 109,92</t>
+          <t>-37,43; 15,55</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-68,62; 12,97</t>
+          <t>-53,74; -4,72</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 22,25</t>
+          <t>2,17; 148,32</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-37,03; 17,51</t>
+          <t>-20,06; 98,64</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-57,57; -10,81</t>
+          <t>-68,82; 11,3</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 54,53</t>
+          <t>-6,07; 54,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 38,59</t>
+          <t>-18,5; 37,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-51,96; -8,55</t>
+          <t>-51,5; -6,46</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5,43</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,63</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-6,01</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>6,66</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-1,17</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-7,14</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5,43</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-6,38</t>
+          <t>-6,91</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-6,59</t>
+          <t>-6,33</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,89; 11,44</t>
+          <t>0,58; 10,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,87</t>
+          <t>-6,39; 2,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,04; -2,05</t>
+          <t>-11,06; -1,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,67; 10,27</t>
+          <t>1,47; 11,22</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 3,03</t>
+          <t>-5,55; 3,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -1,28</t>
+          <t>-11,83; -1,88</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,39; 9,46</t>
+          <t>2,65; 9,66</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 1,8</t>
+          <t>-4,65; 2,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -2,54</t>
+          <t>-9,86; -2,83</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-3,58%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-13,24%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>18,67%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-3,28%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-20,01%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-3,58%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-14,06%</t>
+          <t>-19,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-16,2%</t>
+          <t>-15,55%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5,23; 33,98</t>
+          <t>1,31; 23,82</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 11,63</t>
+          <t>-13,35; 7,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-34,26; -6,24</t>
+          <t>-23,38; -2,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,41; 23,72</t>
+          <t>3,85; 34,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 7,15</t>
+          <t>-14,89; 11,41</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-25,56; -2,94</t>
+          <t>-31,04; -5,46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,54; 24,14</t>
+          <t>6,33; 24,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 4,61</t>
+          <t>-11,01; 6,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-24,75; -6,55</t>
+          <t>-23,4; -7,23</t>
         </is>
       </c>
     </row>
